--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,6 +960,130 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122619577</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57536</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Martinsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>366333</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6624874</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>122619577</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16959134</v>
+        <v>122619577</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,55 +829,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4730</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hagen, 500 m VNV om, Vrm</t>
+          <t>Martinsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>366200.1874100352</v>
+        <v>366333</v>
       </c>
       <c r="R3" t="n">
-        <v>6624833.33645926</v>
+        <v>6624874</v>
       </c>
       <c r="S3" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,34 +897,24 @@
           <t>Gunnarskog</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>S-Arv-0643</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-12-22</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-12-22</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>4 730 bladrosetter med 863 blomstänglar, spridd från 765-957 och 713-969 i öster till 705-891 och 780-862 i väster (RT 90)</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,151 +926,18 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre granskog med inslag av tallar</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Torbjörn Westerberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>122619577</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Martinsmyren, Vrm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>366333</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6624874</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Gunnarskog</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
           <t>Torbjörn Westerberg</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Torbjörn Westerberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +939,216 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125891624</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>klätten-tömme, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>366397</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6624920</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125891570</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57664</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>jaal lon, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>366069</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6624862</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125891624</v>
+        <v>125891570</v>
       </c>
       <c r="B4" t="n">
-        <v>57811</v>
+        <v>57664</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,20 +974,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>klätten-tömme, Vrm</t>
+          <t>jaal lon, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366397</v>
+        <v>366069</v>
       </c>
       <c r="R4" t="n">
-        <v>6624920</v>
+        <v>6624862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125891570</v>
+        <v>125891624</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
+        <v>57811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,20 +1079,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>jaal lon, Vrm</t>
+          <t>klätten-tömme, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>366069</v>
+        <v>366397</v>
       </c>
       <c r="R5" t="n">
-        <v>6624862</v>
+        <v>6624920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125891570</v>
+        <v>125891624</v>
       </c>
       <c r="B4" t="n">
-        <v>57664</v>
+        <v>57811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,20 +974,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>jaal lon, Vrm</t>
+          <t>klätten-tömme, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366069</v>
+        <v>366397</v>
       </c>
       <c r="R4" t="n">
-        <v>6624862</v>
+        <v>6624920</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125891624</v>
+        <v>125891570</v>
       </c>
       <c r="B5" t="n">
-        <v>57811</v>
+        <v>57664</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,20 +1079,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>klätten-tömme, Vrm</t>
+          <t>jaal lon, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>366397</v>
+        <v>366069</v>
       </c>
       <c r="R5" t="n">
-        <v>6624920</v>
+        <v>6624862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125891624</v>
+        <v>125891570</v>
       </c>
       <c r="B4" t="n">
-        <v>57811</v>
+        <v>57665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,20 +974,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>klätten-tömme, Vrm</t>
+          <t>jaal lon, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366397</v>
+        <v>366069</v>
       </c>
       <c r="R4" t="n">
-        <v>6624920</v>
+        <v>6624862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125891570</v>
+        <v>125891624</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
+        <v>57812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,20 +1079,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>jaal lon, Vrm</t>
+          <t>klätten-tömme, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>366069</v>
+        <v>366397</v>
       </c>
       <c r="R5" t="n">
-        <v>6624862</v>
+        <v>6624920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -944,7 +944,7 @@
         <v>125891570</v>
       </c>
       <c r="B4" t="n">
-        <v>57665</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>125891624</v>
       </c>
       <c r="B5" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125891570</v>
+        <v>125891624</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,20 +974,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>jaal lon, Vrm</t>
+          <t>klätten-tömme, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366069</v>
+        <v>366397</v>
       </c>
       <c r="R4" t="n">
-        <v>6624862</v>
+        <v>6624920</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125891624</v>
+        <v>125891570</v>
       </c>
       <c r="B5" t="n">
-        <v>57816</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,20 +1079,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>klätten-tömme, Vrm</t>
+          <t>jaal lon, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>366397</v>
+        <v>366069</v>
       </c>
       <c r="R5" t="n">
-        <v>6624920</v>
+        <v>6624862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125891624</v>
+        <v>125891570</v>
       </c>
       <c r="B4" t="n">
-        <v>57816</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,20 +974,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>klätten-tömme, Vrm</t>
+          <t>jaal lon, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366397</v>
+        <v>366069</v>
       </c>
       <c r="R4" t="n">
-        <v>6624920</v>
+        <v>6624862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125891570</v>
+        <v>125891624</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,20 +1079,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>jaal lon, Vrm</t>
+          <t>klätten-tömme, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>366069</v>
+        <v>366397</v>
       </c>
       <c r="R5" t="n">
-        <v>6624862</v>
+        <v>6624920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -944,7 +944,7 @@
         <v>125891570</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>125891624</v>
       </c>
       <c r="B5" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125891570</v>
+        <v>125891624</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,20 +974,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>jaal lon, Vrm</t>
+          <t>klätten-tömme, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366069</v>
+        <v>366397</v>
       </c>
       <c r="R4" t="n">
-        <v>6624862</v>
+        <v>6624920</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125891624</v>
+        <v>125891570</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>57670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,20 +1079,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>klätten-tömme, Vrm</t>
+          <t>jaal lon, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>366397</v>
+        <v>366069</v>
       </c>
       <c r="R5" t="n">
-        <v>6624920</v>
+        <v>6624862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125891624</v>
+        <v>125891570</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,20 +974,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>klätten-tömme, Vrm</t>
+          <t>jaal lon, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366397</v>
+        <v>366069</v>
       </c>
       <c r="R4" t="n">
-        <v>6624920</v>
+        <v>6624862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125891570</v>
+        <v>125891624</v>
       </c>
       <c r="B5" t="n">
-        <v>57670</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,20 +1079,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>jaal lon, Vrm</t>
+          <t>klätten-tömme, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>366069</v>
+        <v>366397</v>
       </c>
       <c r="R5" t="n">
-        <v>6624862</v>
+        <v>6624920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5936-2025 artfynd.xlsx
+++ b/artfynd/A 5936-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,68 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7095425</v>
+        <v>125891570</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4730</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hagen, 500 m VNV om, Vrm</t>
+          <t>jaal lon, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>366200.7102784767</v>
+        <v>366069</v>
       </c>
       <c r="R2" t="n">
-        <v>6624833.822246583</v>
+        <v>6624862</v>
       </c>
       <c r="S2" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,27 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-12-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-12-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4 730 bladrosetter med 863 blomstänglar, spridd från 765-957 och 713-969 i öster till 705-891 och 780-862 i väster (RT 90)</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,26 +764,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre granskog med inslag av tallar</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Torbjörn Westerberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Torbjörn Westerberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -820,12 +783,7 @@
         <v>122619577</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125891570</v>
+        <v>125891624</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,20 +932,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>jaal lon, Vrm</t>
+          <t>klätten-tömme, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366069</v>
+        <v>366397</v>
       </c>
       <c r="R4" t="n">
-        <v>6624862</v>
+        <v>6624920</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125891624</v>
+        <v>130989759</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,25 +1032,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>klätten-tömme, Vrm</t>
+          <t>jaal lon, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>366397</v>
+        <v>366069</v>
       </c>
       <c r="R5" t="n">
-        <v>6624920</v>
+        <v>6624862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130989759</v>
+        <v>131137190</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,17 +1156,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>jaal lon, Vrm</t>
+          <t>klätten-tömme, Bosebyn, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>366069</v>
+        <v>365991</v>
       </c>
       <c r="R6" t="n">
-        <v>6624862</v>
+        <v>6624939</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,12 +1190,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,6 +1219,263 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7095425</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4730</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hagen, 500 m VNV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>366201</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6624834</v>
+      </c>
+      <c r="S7" t="n">
+        <v>95</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-12-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-12-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4 730 bladrosetter med 863 blomstänglar, spridd från 765-957 och 713-969 i öster till 705-891 och 780-862 i väster (RT 90)</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>äldre granskog med inslag av tallar</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16959134</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4730</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hagen, 500 m VNV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>366200</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6624833</v>
+      </c>
+      <c r="S8" t="n">
+        <v>95</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>S-Arv-0643</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2013-12-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2013-12-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4 730 bladrosetter med 863 blomstänglar, spridd från 765-957 och 713-969 i öster till 705-891 och 780-862 i väster (RT 90)</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre granskog med inslag av tallar</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
